--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59551,6 +59551,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2574">
+      <c r="A2574" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2574" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2574" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="D2574" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="E2574" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59574,6 +59574,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>644</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59597,6 +59597,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59461,22 +59461,22 @@
     </row>
     <row r="2570">
       <c r="A2570" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2570" t="n">
-        <v>1047</v>
+        <v>1529</v>
       </c>
       <c r="C2570" t="n">
-        <v>25.3999996185303</v>
+        <v>24.8999996185303</v>
       </c>
       <c r="D2570" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E2570" t="n">
         <v>24.5</v>
       </c>
       <c r="F2570" t="n">
-        <v>24.8999996185303</v>
+        <v>24.2000007629395</v>
       </c>
       <c r="G2570" t="s">
         <v>7</v>
@@ -59484,22 +59484,22 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2571" t="n">
-        <v>937</v>
+        <v>1047</v>
       </c>
       <c r="C2571" t="n">
-        <v>25.6000003814697</v>
+        <v>25.3999996185303</v>
       </c>
       <c r="D2571" t="n">
-        <v>25.3999996185303</v>
+        <v>24.5</v>
       </c>
       <c r="E2571" t="n">
-        <v>25.6000003814697</v>
+        <v>24.5</v>
       </c>
       <c r="F2571" t="n">
-        <v>25.6000003814697</v>
+        <v>24.8999996185303</v>
       </c>
       <c r="G2571" t="s">
         <v>7</v>
@@ -59507,22 +59507,22 @@
     </row>
     <row r="2572">
       <c r="A2572" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2572" t="n">
-        <v>300</v>
+        <v>937</v>
       </c>
       <c r="C2572" t="n">
-        <v>26.2000007629395</v>
+        <v>25.6000003814697</v>
       </c>
       <c r="D2572" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="E2572" t="n">
         <v>25.6000003814697</v>
       </c>
-      <c r="E2572" t="n">
-        <v>25.7000007629395</v>
-      </c>
       <c r="F2572" t="n">
-        <v>26.2000007629395</v>
+        <v>25.6000003814697</v>
       </c>
       <c r="G2572" t="s">
         <v>7</v>
@@ -59530,22 +59530,22 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2573" t="n">
-        <v>1433</v>
+        <v>300</v>
       </c>
       <c r="C2573" t="n">
-        <v>26.2999992370605</v>
+        <v>26.2000007629395</v>
       </c>
       <c r="D2573" t="n">
-        <v>25.3999996185303</v>
+        <v>25.6000003814697</v>
       </c>
       <c r="E2573" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="F2573" t="n">
         <v>26.2000007629395</v>
-      </c>
-      <c r="F2573" t="n">
-        <v>26.2999992370605</v>
       </c>
       <c r="G2573" t="s">
         <v>7</v>
@@ -59553,19 +59553,19 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2574" t="n">
-        <v>500</v>
+        <v>1433</v>
       </c>
       <c r="C2574" t="n">
         <v>26.2999992370605</v>
       </c>
       <c r="D2574" t="n">
-        <v>26.2999992370605</v>
+        <v>25.3999996185303</v>
       </c>
       <c r="E2574" t="n">
-        <v>26.2999992370605</v>
+        <v>26.2000007629395</v>
       </c>
       <c r="F2574" t="n">
         <v>26.2999992370605</v>
@@ -59576,22 +59576,22 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2575" t="n">
-        <v>644</v>
+        <v>500</v>
       </c>
       <c r="C2575" t="n">
-        <v>26</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="D2575" t="n">
-        <v>25.5</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="E2575" t="n">
-        <v>25.8999996185303</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="F2575" t="n">
-        <v>25.5</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="G2575" t="s">
         <v>7</v>
@@ -59599,24 +59599,70 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2576" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="C2576" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="D2576" t="n">
         <v>25.5</v>
       </c>
       <c r="E2576" t="n">
-        <v>25.5</v>
+        <v>25.8999996185303</v>
       </c>
       <c r="F2576" t="n">
         <v>25.5</v>
       </c>
       <c r="G2576" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>1196</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="G2578" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67455,6 +67455,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>1467</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>26.3999996185303</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2581" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2581" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67481,6 +67481,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>443</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>26.3999996185303</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>26.1000003814697</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="G2582" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="H2582" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67507,6 +67507,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>510</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="G2583" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="H2583" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67533,6 +67533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>2670</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="G2584" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="H2584" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67611,6 +67611,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2587">
+      <c r="A2587" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2587" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C2587" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2587" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="E2587" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2587" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2587" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H2587" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59935,8 +59935,31 @@
       <c r="E2590" t="n">
         <v>24.7000007629395</v>
       </c>
-      <c r="F2590"/>
+      <c r="F2590" t="n">
+        <v>24.7999992370605</v>
+      </c>
       <c r="G2590" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>160</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="F2591"/>
+      <c r="G2591" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59958,8 +59958,31 @@
       <c r="E2591" t="n">
         <v>24.7999992370605</v>
       </c>
-      <c r="F2591"/>
+      <c r="F2591" t="n">
+        <v>24.7000007629395</v>
+      </c>
       <c r="G2591" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>439</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="F2592"/>
+      <c r="G2592" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -59981,8 +59981,31 @@
       <c r="E2592" t="n">
         <v>24.7000007629395</v>
       </c>
-      <c r="F2592"/>
+      <c r="F2592" t="n">
+        <v>24.2999992370605</v>
+      </c>
       <c r="G2592" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>622</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="F2593"/>
+      <c r="G2593" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -60004,8 +60004,31 @@
       <c r="E2593" t="n">
         <v>24.3999996185303</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G2593" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>562</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="F2594"/>
+      <c r="G2594" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -60034,6 +60034,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>980</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67897,6 +67897,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2598">
+      <c r="A2598" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2598" t="n">
+        <v>638</v>
+      </c>
+      <c r="C2598" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="D2598" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="E2598" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="G2598" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="H2598" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -67923,6 +67923,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2599">
+      <c r="A2599" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2599" t="n">
+        <v>1163</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="D2599" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="E2599" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="G2599" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="H2599" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75778,6 +75778,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2601">
+      <c r="A2601" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2601" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2601" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2601" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2601" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="G2601" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="H2601" t="n">
+        <v>3077</v>
+      </c>
+      <c r="I2601" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75807,6 +75807,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2602">
+      <c r="A2602" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2602" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2602" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2602" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2602" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="G2602" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="H2602" t="n">
+        <v>69</v>
+      </c>
+      <c r="I2602" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75836,6 +75836,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2603" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2603" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="G2603" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="H2603" t="n">
+        <v>1327</v>
+      </c>
+      <c r="I2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75865,6 +75865,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2604">
+      <c r="A2604" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2604" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2604" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="D2604" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2604" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2604" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="G2604" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="H2604" t="n">
+        <v>428</v>
+      </c>
+      <c r="I2604" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75894,6 +75894,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2605">
+      <c r="A2605" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2605" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2605" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="G2605" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="H2605" t="n">
+        <v>402</v>
+      </c>
+      <c r="I2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75908,7 +75908,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="E2605" t="n">
-        <v>21.2999992370605</v>
+        <v>21.2000007629395</v>
       </c>
       <c r="F2605" t="n">
         <v>21.2000007629395</v>
@@ -75920,6 +75920,35 @@
         <v>402</v>
       </c>
       <c r="I2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2606" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2606" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="G2606" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="H2606" t="n">
+        <v>192</v>
+      </c>
+      <c r="I2606" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75952,6 +75952,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2607">
+      <c r="A2607" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2607" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2607" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D2607" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2607" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F2607" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G2607" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="H2607" t="n">
+        <v>458</v>
+      </c>
+      <c r="I2607" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -75981,6 +75981,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2608">
+      <c r="A2608" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2608" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2608" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2608" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E2608" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2608" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G2608" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H2608" t="n">
+        <v>665</v>
+      </c>
+      <c r="I2608" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DHH.MI.xlsx
+++ b/data/DHH.MI.xlsx
@@ -76010,6 +76010,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2609">
+      <c r="A2609" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2609" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2609" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="D2609" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="E2609" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="G2609" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="H2609" t="n">
+        <v>2642</v>
+      </c>
+      <c r="I2609" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
